--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/pre LAM_HRM-2031-0312/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.89664</v>
+        <v>18.05792</v>
       </c>
       <c r="D2" t="n">
-        <v>17.72141</v>
+        <v>17.45793</v>
       </c>
       <c r="E2" t="n">
-        <v>17.74375</v>
+        <v>17.68081</v>
       </c>
       <c r="F2" t="n">
-        <v>44.43818</v>
+        <v>45.35005</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0549</v>
+        <v>0.05339</v>
       </c>
       <c r="H2" t="n">
-        <v>1.96171</v>
+        <v>1.88925</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.95487</v>
+        <v>17.77398</v>
       </c>
       <c r="D3" t="n">
-        <v>17.87112</v>
+        <v>17.44739</v>
       </c>
       <c r="E3" t="n">
-        <v>17.79019</v>
+        <v>17.73164</v>
       </c>
       <c r="F3" t="n">
-        <v>45.42397</v>
+        <v>45.68376</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0539</v>
+        <v>0.05376</v>
       </c>
       <c r="H3" t="n">
-        <v>1.95578</v>
+        <v>1.95289</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.88047</v>
+        <v>18.14106</v>
       </c>
       <c r="D4" t="n">
-        <v>17.33097</v>
+        <v>17.61647</v>
       </c>
       <c r="E4" t="n">
-        <v>18.00183</v>
+        <v>18.06065</v>
       </c>
       <c r="F4" t="n">
-        <v>45.99669</v>
+        <v>44.07145</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0545</v>
+        <v>0.055</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93355</v>
+        <v>1.90938</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.36005</v>
+        <v>17.95841</v>
       </c>
       <c r="D6" t="n">
-        <v>16.86883</v>
+        <v>17.01377</v>
       </c>
       <c r="E6" t="n">
-        <v>17.30182</v>
+        <v>17.65348</v>
       </c>
       <c r="F6" t="n">
-        <v>23.27305</v>
+        <v>23.18453</v>
       </c>
       <c r="G6" t="n">
-        <v>36.65256</v>
+        <v>36.19579</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.52724</v>
+        <v>17.73697</v>
       </c>
       <c r="D7" t="n">
-        <v>17.06418</v>
+        <v>16.67487</v>
       </c>
       <c r="E7" t="n">
-        <v>17.67573</v>
+        <v>17.43152</v>
       </c>
       <c r="F7" t="n">
-        <v>22.92012</v>
+        <v>23.14934</v>
       </c>
       <c r="G7" t="n">
-        <v>36.06605</v>
+        <v>36.18003</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.43992</v>
+        <v>17.67559</v>
       </c>
       <c r="D8" t="n">
-        <v>16.8594</v>
+        <v>16.54718</v>
       </c>
       <c r="E8" t="n">
-        <v>17.55244</v>
+        <v>17.19505</v>
       </c>
       <c r="F8" t="n">
-        <v>23.4125</v>
+        <v>22.87315</v>
       </c>
       <c r="G8" t="n">
-        <v>36.33188</v>
+        <v>36.84184</v>
       </c>
     </row>
   </sheetData>
